--- a/tracker/2250823/Filter_Order_Log.xlsx
+++ b/tracker/2250823/Filter_Order_Log.xlsx
@@ -45,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,11 +69,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +488,11 @@
           <t>Phase</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>None (single phase for now)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -515,72 +519,72 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Order date</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Filter set (1/2/3/Attic)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Vendor SO #</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Our PO #</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>MERV</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Order total price</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Line total</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Units it went to</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Delivery</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -615,7 +619,7 @@
       <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>98.23999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
@@ -626,14 +630,14 @@
       <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="3" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <f>I8*J8</f>
         <v/>
       </c>
-      <c r="L8" s="2" t="n"/>
+      <c r="L8" s="4" t="n"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Customer pickup</t>
@@ -674,7 +678,7 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>20x20x4</t>
@@ -683,14 +687,14 @@
       <c r="I9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="3" t="n">
         <v>7.46</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <f>I9*J9</f>
         <v/>
       </c>
-      <c r="L9" s="2" t="n"/>
+      <c r="L9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -721,7 +725,7 @@
       <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="3" t="n">
         <v>368.44</v>
       </c>
       <c r="H10" t="inlineStr">
@@ -732,14 +736,14 @@
       <c r="I10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="3" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <f>I10*J10</f>
         <v/>
       </c>
-      <c r="L10" s="2" t="n"/>
+      <c r="L10" s="4" t="n"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Delivered 2026-10-09</t>
@@ -780,7 +784,7 @@
       <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>20x25x2</t>
@@ -789,14 +793,14 @@
       <c r="I11" t="n">
         <v>24</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="3" t="n">
         <v>4.83</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="3">
         <f>I11*J11</f>
         <v/>
       </c>
-      <c r="L11" s="2" t="n"/>
+      <c r="L11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -827,7 +831,7 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="3" t="n"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>20x20x4</t>
@@ -836,14 +840,14 @@
       <c r="I12" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="3" t="n">
         <v>7.46</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <f>I12*J12</f>
         <v/>
       </c>
-      <c r="L12" s="2" t="n"/>
+      <c r="L12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -874,7 +878,7 @@
       <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>20x20x2</t>
@@ -883,14 +887,14 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <f>I13*J13</f>
         <v/>
       </c>
-      <c r="L13" s="2" t="n"/>
+      <c r="L13" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -914,27 +918,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Ordered (all orders)</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Needed - units replaced</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Left over (+) / Short (-)</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Still needed - units not yet replaced</t>
         </is>

--- a/tracker/2250823/Filter_Order_Log.xlsx
+++ b/tracker/2250823/Filter_Order_Log.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>QTY</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
